--- a/Lab_python/lab4_new/lab4.5_new/lab4.5_new/рост_по_точкам.xlsx
+++ b/Lab_python/lab4_new/lab4.5_new/lab4.5_new/рост_по_точкам.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-22.5</v>
+        <v>4.5</v>
       </c>
       <c r="C2" t="n">
-        <v>-14.5</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-8.699999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.9</v>
+        <v>-0.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3</v>
+        <v>-2.5</v>
       </c>
     </row>
   </sheetData>

--- a/Lab_python/lab4_new/lab4.5_new/lab4.5_new/рост_по_точкам.xlsx
+++ b/Lab_python/lab4_new/lab4.5_new/lab4.5_new/рост_по_точкам.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.5</v>
+        <v>-11.7</v>
       </c>
       <c r="C2" t="n">
-        <v>14.4</v>
+        <v>-21.1</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5</v>
+        <v>-52.9</v>
       </c>
       <c r="C3" t="n">
-        <v>11.5</v>
+        <v>-44.9</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.2</v>
+        <v>64.8</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.5</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
   </sheetData>
